--- a/e2e-screenshots/todays-fixes/fixtures/FIXVERIFY_INVENTORY.xlsx
+++ b/e2e-screenshots/todays-fixes/fixtures/FIXVERIFY_INVENTORY.xlsx
@@ -436,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="B2" t="str">
         <v>FIXVERIFY 12</v>
@@ -471,7 +471,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="B3" t="str">
         <v>FIXVERIFY 12</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="B4" t="str">
         <v>FIXVERIFY 12</v>
@@ -541,7 +541,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="B5" t="str">
         <v>FIXVERIFY 15</v>
@@ -576,7 +576,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="B6" t="str">
         <v>FIXVERIFY 15</v>
@@ -611,7 +611,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="B7" t="str">
         <v>FIXVERIFY 15</v>
@@ -646,7 +646,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="B8" t="str">
         <v>FIXVERIFY 15</v>
@@ -681,7 +681,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="B9" t="str">
         <v>FIXVERIFY 15</v>
@@ -716,7 +716,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="B10" t="str">
         <v>FIXVERIFY 15</v>
@@ -751,7 +751,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="B11" t="str">
         <v>FIXVERIFY 15</v>

--- a/e2e-screenshots/todays-fixes/fixtures/FIXVERIFY_INVENTORY.xlsx
+++ b/e2e-screenshots/todays-fixes/fixtures/FIXVERIFY_INVENTORY.xlsx
@@ -436,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-06-07</v>
+        <v>2026-06-08</v>
       </c>
       <c r="B2" t="str">
         <v>FIXVERIFY 12</v>
@@ -471,7 +471,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-06-07</v>
+        <v>2026-06-08</v>
       </c>
       <c r="B3" t="str">
         <v>FIXVERIFY 12</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-06-07</v>
+        <v>2026-06-08</v>
       </c>
       <c r="B4" t="str">
         <v>FIXVERIFY 12</v>
@@ -541,7 +541,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-06-07</v>
+        <v>2026-06-08</v>
       </c>
       <c r="B5" t="str">
         <v>FIXVERIFY 15</v>
@@ -576,7 +576,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-06-07</v>
+        <v>2026-06-08</v>
       </c>
       <c r="B6" t="str">
         <v>FIXVERIFY 15</v>
@@ -611,7 +611,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-06-07</v>
+        <v>2026-06-08</v>
       </c>
       <c r="B7" t="str">
         <v>FIXVERIFY 15</v>
@@ -646,7 +646,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-06-07</v>
+        <v>2026-06-08</v>
       </c>
       <c r="B8" t="str">
         <v>FIXVERIFY 15</v>
@@ -681,7 +681,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-06-07</v>
+        <v>2026-06-08</v>
       </c>
       <c r="B9" t="str">
         <v>FIXVERIFY 15</v>
@@ -716,7 +716,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-06-07</v>
+        <v>2026-06-08</v>
       </c>
       <c r="B10" t="str">
         <v>FIXVERIFY 15</v>
@@ -751,7 +751,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-06-07</v>
+        <v>2026-06-08</v>
       </c>
       <c r="B11" t="str">
         <v>FIXVERIFY 15</v>

--- a/e2e-screenshots/todays-fixes/fixtures/FIXVERIFY_INVENTORY.xlsx
+++ b/e2e-screenshots/todays-fixes/fixtures/FIXVERIFY_INVENTORY.xlsx
@@ -436,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="B2" t="str">
         <v>FIXVERIFY 12</v>
@@ -471,7 +471,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="B3" t="str">
         <v>FIXVERIFY 12</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="B4" t="str">
         <v>FIXVERIFY 12</v>
@@ -541,7 +541,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="B5" t="str">
         <v>FIXVERIFY 15</v>
@@ -576,7 +576,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="B6" t="str">
         <v>FIXVERIFY 15</v>
@@ -611,7 +611,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="B7" t="str">
         <v>FIXVERIFY 15</v>
@@ -646,7 +646,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="B8" t="str">
         <v>FIXVERIFY 15</v>
@@ -681,7 +681,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="B9" t="str">
         <v>FIXVERIFY 15</v>
@@ -716,7 +716,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="B10" t="str">
         <v>FIXVERIFY 15</v>
@@ -751,7 +751,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="B11" t="str">
         <v>FIXVERIFY 15</v>

--- a/e2e-screenshots/todays-fixes/fixtures/FIXVERIFY_INVENTORY.xlsx
+++ b/e2e-screenshots/todays-fixes/fixtures/FIXVERIFY_INVENTORY.xlsx
@@ -436,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-12</v>
       </c>
       <c r="B2" t="str">
         <v>FIXVERIFY 12</v>
@@ -471,7 +471,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-12</v>
       </c>
       <c r="B3" t="str">
         <v>FIXVERIFY 12</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-12</v>
       </c>
       <c r="B4" t="str">
         <v>FIXVERIFY 12</v>
@@ -541,7 +541,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-12</v>
       </c>
       <c r="B5" t="str">
         <v>FIXVERIFY 15</v>
@@ -576,7 +576,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-12</v>
       </c>
       <c r="B6" t="str">
         <v>FIXVERIFY 15</v>
@@ -611,7 +611,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-12</v>
       </c>
       <c r="B7" t="str">
         <v>FIXVERIFY 15</v>
@@ -646,7 +646,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-12</v>
       </c>
       <c r="B8" t="str">
         <v>FIXVERIFY 15</v>
@@ -681,7 +681,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-12</v>
       </c>
       <c r="B9" t="str">
         <v>FIXVERIFY 15</v>
@@ -716,7 +716,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-12</v>
       </c>
       <c r="B10" t="str">
         <v>FIXVERIFY 15</v>
@@ -751,7 +751,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-12</v>
       </c>
       <c r="B11" t="str">
         <v>FIXVERIFY 15</v>

--- a/e2e-screenshots/todays-fixes/fixtures/FIXVERIFY_INVENTORY.xlsx
+++ b/e2e-screenshots/todays-fixes/fixtures/FIXVERIFY_INVENTORY.xlsx
@@ -436,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-06-12</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B2" t="str">
         <v>FIXVERIFY 12</v>
@@ -471,7 +471,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-06-12</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B3" t="str">
         <v>FIXVERIFY 12</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-06-12</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B4" t="str">
         <v>FIXVERIFY 12</v>
@@ -541,7 +541,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-06-12</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B5" t="str">
         <v>FIXVERIFY 15</v>
@@ -576,7 +576,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-06-12</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B6" t="str">
         <v>FIXVERIFY 15</v>
@@ -611,7 +611,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-06-12</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B7" t="str">
         <v>FIXVERIFY 15</v>
@@ -646,7 +646,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-06-12</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B8" t="str">
         <v>FIXVERIFY 15</v>
@@ -681,7 +681,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-06-12</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B9" t="str">
         <v>FIXVERIFY 15</v>
@@ -716,7 +716,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-06-12</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B10" t="str">
         <v>FIXVERIFY 15</v>
@@ -751,7 +751,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-06-12</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B11" t="str">
         <v>FIXVERIFY 15</v>

--- a/e2e-screenshots/todays-fixes/fixtures/FIXVERIFY_INVENTORY.xlsx
+++ b/e2e-screenshots/todays-fixes/fixtures/FIXVERIFY_INVENTORY.xlsx
@@ -436,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-11</v>
       </c>
       <c r="B2" t="str">
         <v>FIXVERIFY 12</v>
@@ -471,7 +471,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-11</v>
       </c>
       <c r="B3" t="str">
         <v>FIXVERIFY 12</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-11</v>
       </c>
       <c r="B4" t="str">
         <v>FIXVERIFY 12</v>
@@ -541,7 +541,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-11</v>
       </c>
       <c r="B5" t="str">
         <v>FIXVERIFY 15</v>
@@ -576,7 +576,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-11</v>
       </c>
       <c r="B6" t="str">
         <v>FIXVERIFY 15</v>
@@ -611,7 +611,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-11</v>
       </c>
       <c r="B7" t="str">
         <v>FIXVERIFY 15</v>
@@ -646,7 +646,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-11</v>
       </c>
       <c r="B8" t="str">
         <v>FIXVERIFY 15</v>
@@ -681,7 +681,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-11</v>
       </c>
       <c r="B9" t="str">
         <v>FIXVERIFY 15</v>
@@ -716,7 +716,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-11</v>
       </c>
       <c r="B10" t="str">
         <v>FIXVERIFY 15</v>
@@ -751,7 +751,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-11</v>
       </c>
       <c r="B11" t="str">
         <v>FIXVERIFY 15</v>
